--- a/public/database/Usuarios.xlsx
+++ b/public/database/Usuarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ignacio Aguilera\Desktop\Trabajo (SPA)\rosmiya\public\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ignacio Aguilera\Desktop\Trabajo (SPA)\happyhomeandgoods\public\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77256896-D98F-4766-933A-99F687C4F95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A1DA3F-BBC9-4D52-8776-8C3EEE277590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D68F4056-0D45-4BC6-8B04-16C26C5398A7}"/>
+    <workbookView xWindow="-18288" yWindow="1992" windowWidth="17280" windowHeight="8880" xr2:uid="{D68F4056-0D45-4BC6-8B04-16C26C5398A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
@@ -45,21 +45,12 @@
     <t>admin</t>
   </si>
   <si>
-    <t>msanchez</t>
-  </si>
-  <si>
-    <t>$2b$10$q5gm7WVXEB/mSyhVBB72Je6JOBAa9cQu6E7ATmviA0XFnKB.qhaqW</t>
-  </si>
-  <si>
     <t>nombre</t>
   </si>
   <si>
     <t>Administrador</t>
   </si>
   <si>
-    <t>Maivelyn Sanchez</t>
-  </si>
-  <si>
     <t>$2b$10$7JyEmv1DMcHUfsKb/JagS.j4Vrzh/hvOTBN7JeVZF2Ry2R4G8v4IG</t>
   </si>
   <si>
@@ -75,19 +66,28 @@
     <t>alias</t>
   </si>
   <si>
-    <t>Maicita</t>
-  </si>
-  <si>
-    <t>yane</t>
-  </si>
-  <si>
-    <t>$2b$10$zFA0mn/jvB3DPE2UpcmCH.myv6ZerFjelthq1NYHRJtrFMZJBUNba</t>
-  </si>
-  <si>
-    <t>Yaneria Sanchez</t>
-  </si>
-  <si>
-    <t>Yane</t>
+    <t>msalas</t>
+  </si>
+  <si>
+    <t>Mauricio Salas</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t>$2b$10$sbhCFn3ezeF3GyivqSaYXuPz/D3Vntxu0s1xCY/kpAlJvT84GxP.G</t>
+  </si>
+  <si>
+    <t>Constanza</t>
+  </si>
+  <si>
+    <t>csoza</t>
+  </si>
+  <si>
+    <t>Constanza Soza</t>
+  </si>
+  <si>
+    <t>$2b$10$pxeuawAvAvGSuOOoB1H9YOuQVw2vinPIhpIzkez.GOKZt8h3b995C</t>
   </si>
 </sst>
 </file>
@@ -454,13 +454,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A9B6F27-5EFA-4ABC-AF87-8DE32F38EB28}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="66.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,66 +468,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
